--- a/Exp3_PTO_GRPO/eda/results/arms/training/tables/claude-haiku-4-5/training.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/training/tables/claude-haiku-4-5/training.xlsx
@@ -453,7 +453,7 @@
         <v>0.7599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7988</v>
+        <v>0.804</v>
       </c>
       <c r="D2" t="n">
         <v>0.8037</v>
@@ -470,7 +470,7 @@
         <v>0.7707000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8129</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0.8037</v>
@@ -487,7 +487,7 @@
         <v>0.7736</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8085</v>
+        <v>0.8144</v>
       </c>
       <c r="D4" t="n">
         <v>0.7961</v>
@@ -504,7 +504,7 @@
         <v>0.7562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8073</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0.7883</v>
@@ -521,7 +521,7 @@
         <v>0.7474</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8105</v>
+        <v>0.8141</v>
       </c>
       <c r="D6" t="n">
         <v>0.7758</v>
@@ -538,7 +538,7 @@
         <v>0.7359</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8095</v>
+        <v>0.8118</v>
       </c>
       <c r="D7" t="n">
         <v>0.7708</v>
@@ -555,7 +555,7 @@
         <v>0.7292999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8165</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0.7534999999999999</v>
@@ -572,7 +572,7 @@
         <v>0.7281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8138</v>
+        <v>0.8179</v>
       </c>
       <c r="D9" t="n">
         <v>0.7468</v>
@@ -589,7 +589,7 @@
         <v>0.7211</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8185</v>
+        <v>0.8189</v>
       </c>
       <c r="D10" t="n">
         <v>0.7413</v>
@@ -606,7 +606,7 @@
         <v>0.7229</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8127</v>
+        <v>0.8157</v>
       </c>
       <c r="D11" t="n">
         <v>0.7168</v>
@@ -623,7 +623,7 @@
         <v>0.7131</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8108</v>
+        <v>0.8123</v>
       </c>
       <c r="D12" t="n">
         <v>0.7224</v>
@@ -640,7 +640,7 @@
         <v>0.7138</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8177</v>
+        <v>0.8197</v>
       </c>
       <c r="D13" t="n">
         <v>0.7217</v>
@@ -657,7 +657,7 @@
         <v>0.7222</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8245</v>
+        <v>0.8252</v>
       </c>
       <c r="D14" t="n">
         <v>0.7277</v>
@@ -674,7 +674,7 @@
         <v>0.709</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8263</v>
+        <v>0.829</v>
       </c>
       <c r="D15" t="n">
         <v>0.7292</v>
@@ -691,7 +691,7 @@
         <v>0.7144</v>
       </c>
       <c r="C16" t="n">
-        <v>0.835</v>
+        <v>0.8378</v>
       </c>
       <c r="D16" t="n">
         <v>0.7262999999999999</v>
@@ -708,7 +708,7 @@
         <v>0.7217</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8306</v>
+        <v>0.8328</v>
       </c>
       <c r="D17" t="n">
         <v>0.7118</v>
@@ -725,7 +725,7 @@
         <v>0.7102000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8234</v>
+        <v>0.8259</v>
       </c>
       <c r="D18" t="n">
         <v>0.7069</v>
@@ -742,7 +742,7 @@
         <v>0.7093</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8244</v>
+        <v>0.8272</v>
       </c>
       <c r="D19" t="n">
         <v>0.7036</v>
@@ -759,7 +759,7 @@
         <v>0.7171</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8229</v>
+        <v>0.8247</v>
       </c>
       <c r="D20" t="n">
         <v>0.7027</v>
@@ -776,7 +776,7 @@
         <v>0.7189</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8361</v>
+        <v>0.8359</v>
       </c>
     </row>
   </sheetData>
@@ -1145,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7988121004681129</v>
+        <v>0.8040124095139607</v>
       </c>
       <c r="D22" t="n">
-        <v>19867</v>
+        <v>24175</v>
       </c>
     </row>
     <row r="23">
@@ -1161,10 +1161,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8129091104195729</v>
+        <v>0.8169719330610093</v>
       </c>
       <c r="D23" t="n">
-        <v>18638</v>
+        <v>22767</v>
       </c>
     </row>
     <row r="24">
@@ -1177,10 +1177,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.80850939310587</v>
+        <v>0.814419878693015</v>
       </c>
       <c r="D24" t="n">
-        <v>17087</v>
+        <v>20444</v>
       </c>
     </row>
     <row r="25">
@@ -1193,10 +1193,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.807252440725244</v>
+        <v>0.813967635965446</v>
       </c>
       <c r="D25" t="n">
-        <v>14340</v>
+        <v>16438</v>
       </c>
     </row>
     <row r="26">
@@ -1209,10 +1209,10 @@
         <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8105263157894737</v>
+        <v>0.8141448645291515</v>
       </c>
       <c r="D26" t="n">
-        <v>11685</v>
+        <v>12881</v>
       </c>
     </row>
     <row r="27">
@@ -1225,10 +1225,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8094816127603013</v>
+        <v>0.8118179946469014</v>
       </c>
       <c r="D27" t="n">
-        <v>9028</v>
+        <v>9714</v>
       </c>
     </row>
     <row r="28">
@@ -1241,10 +1241,10 @@
         <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8164604144923214</v>
+        <v>0.817021873247336</v>
       </c>
       <c r="D28" t="n">
-        <v>6707</v>
+        <v>7132</v>
       </c>
     </row>
     <row r="29">
@@ -1257,10 +1257,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8138051044083526</v>
+        <v>0.8178838098706975</v>
       </c>
       <c r="D29" t="n">
-        <v>5172</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="30">
@@ -1273,10 +1273,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8184537505752416</v>
+        <v>0.8188976377952756</v>
       </c>
       <c r="D30" t="n">
-        <v>4346</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="31">
@@ -1289,10 +1289,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8127362605408549</v>
+        <v>0.8156643356643357</v>
       </c>
       <c r="D31" t="n">
-        <v>3439</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="32">
@@ -1305,10 +1305,10 @@
         <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8108424336973479</v>
+        <v>0.8122634367903103</v>
       </c>
       <c r="D32" t="n">
-        <v>2564</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="33">
@@ -1321,10 +1321,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8177339901477833</v>
+        <v>0.8196642685851319</v>
       </c>
       <c r="D33" t="n">
-        <v>2030</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="34">
@@ -1337,10 +1337,10 @@
         <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8245125348189415</v>
+        <v>0.8252321135991262</v>
       </c>
       <c r="D34" t="n">
-        <v>1795</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="35">
@@ -1353,10 +1353,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8263305322128851</v>
+        <v>0.8289835164835165</v>
       </c>
       <c r="D35" t="n">
-        <v>1428</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="36">
@@ -1369,10 +1369,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8350353495679497</v>
+        <v>0.8378170637970792</v>
       </c>
       <c r="D36" t="n">
-        <v>1273</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="37">
@@ -1385,10 +1385,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8305821025195482</v>
+        <v>0.8327645051194539</v>
       </c>
       <c r="D37" t="n">
-        <v>1151</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="38">
@@ -1401,10 +1401,10 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8233590733590733</v>
+        <v>0.825922421948912</v>
       </c>
       <c r="D38" t="n">
-        <v>1036</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="39">
@@ -1417,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8243953732912723</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="D39" t="n">
-        <v>951</v>
+        <v>972</v>
       </c>
     </row>
     <row r="40">
@@ -1433,10 +1433,10 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8228941684665226</v>
+        <v>0.824654622741764</v>
       </c>
       <c r="D40" t="n">
-        <v>926</v>
+        <v>941</v>
       </c>
     </row>
     <row r="41">
@@ -1449,10 +1449,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8361244019138756</v>
+        <v>0.835909631391201</v>
       </c>
       <c r="D41" t="n">
-        <v>836</v>
+        <v>841</v>
       </c>
     </row>
     <row r="42">
@@ -2074,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,26 +2492,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>3.290739216204042</v>
+        <v>3.869958969082514</v>
       </c>
       <c r="D17" t="n">
-        <v>7592</v>
+        <v>9376</v>
       </c>
       <c r="E17" t="n">
-        <v>1.829718137254902</v>
+        <v>2.797671568627451</v>
       </c>
       <c r="F17" t="n">
         <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>1.46102107894914</v>
+        <v>1.072287400455063</v>
       </c>
     </row>
     <row r="18">
@@ -2521,22 +2521,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3.33243209735256</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="D18" t="n">
-        <v>6176</v>
+        <v>7592</v>
       </c>
       <c r="E18" t="n">
-        <v>2.071568627450981</v>
+        <v>1.829718137254902</v>
       </c>
       <c r="F18" t="n">
         <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>1.260863469901579</v>
+        <v>1.46102107894914</v>
       </c>
     </row>
     <row r="19">
@@ -2546,22 +2546,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3.536591102906034</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="D19" t="n">
-        <v>6296</v>
+        <v>6176</v>
       </c>
       <c r="E19" t="n">
-        <v>2.199203431372549</v>
+        <v>2.071568627450981</v>
       </c>
       <c r="F19" t="n">
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>1.337387671533485</v>
+        <v>1.260863469901579</v>
       </c>
     </row>
     <row r="20">
@@ -2571,22 +2571,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>3.663854489164087</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="D20" t="n">
-        <v>5176</v>
+        <v>6296</v>
       </c>
       <c r="E20" t="n">
-        <v>2.480208333333333</v>
+        <v>2.199203431372549</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>1.183646155830754</v>
+        <v>1.337387671533485</v>
       </c>
     </row>
     <row r="21">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>3.743944564470195</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="D21" t="n">
-        <v>4800</v>
+        <v>5176</v>
       </c>
       <c r="E21" t="n">
-        <v>2.680453431372549</v>
+        <v>2.480208333333333</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>1.063491133097647</v>
+        <v>1.183646155830754</v>
       </c>
     </row>
     <row r="22">
@@ -2621,22 +2621,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3.776677555295115</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="D22" t="n">
-        <v>4728</v>
+        <v>4800</v>
       </c>
       <c r="E22" t="n">
-        <v>2.751960784313725</v>
+        <v>2.680453431372549</v>
       </c>
       <c r="F22" t="n">
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>1.024716770981389</v>
+        <v>1.063491133097647</v>
       </c>
     </row>
     <row r="23">
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>3.889255298078827</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="D23" t="n">
-        <v>4168</v>
+        <v>4728</v>
       </c>
       <c r="E23" t="n">
-        <v>2.849571078431373</v>
+        <v>2.751960784313725</v>
       </c>
       <c r="F23" t="n">
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>1.039684219647455</v>
+        <v>1.024716770981389</v>
       </c>
     </row>
     <row r="24">
@@ -2671,22 +2671,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>4.005326146015042</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="D24" t="n">
-        <v>4136</v>
+        <v>4168</v>
       </c>
       <c r="E24" t="n">
-        <v>2.813235294117647</v>
+        <v>2.849571078431373</v>
       </c>
       <c r="F24" t="n">
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>1.192090851897395</v>
+        <v>1.039684219647455</v>
       </c>
     </row>
     <row r="25">
@@ -2696,22 +2696,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>3.999240719910011</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="D25" t="n">
-        <v>3568</v>
+        <v>4136</v>
       </c>
       <c r="E25" t="n">
-        <v>2.895465686274509</v>
+        <v>2.813235294117647</v>
       </c>
       <c r="F25" t="n">
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>1.103775033635502</v>
+        <v>1.192090851897395</v>
       </c>
     </row>
     <row r="26">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>4.077670148096037</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="D26" t="n">
-        <v>3280</v>
+        <v>3568</v>
       </c>
       <c r="E26" t="n">
-        <v>2.921078431372549</v>
+        <v>2.895465686274509</v>
       </c>
       <c r="F26" t="n">
         <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>1.156591716723488</v>
+        <v>1.103775033635502</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>3.291063332476854</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="D27" t="n">
-        <v>7120</v>
+        <v>3280</v>
       </c>
       <c r="E27" t="n">
-        <v>1.833700980392157</v>
+        <v>2.921078431372549</v>
       </c>
       <c r="F27" t="n">
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>1.457362352084697</v>
+        <v>1.156591716723488</v>
       </c>
     </row>
     <row r="28">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3.473938140701307</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="D28" t="n">
-        <v>6696</v>
+        <v>7120</v>
       </c>
       <c r="E28" t="n">
-        <v>2.011519607843137</v>
+        <v>1.833700980392157</v>
       </c>
       <c r="F28" t="n">
         <v>96</v>
       </c>
       <c r="G28" t="n">
-        <v>1.46241853285817</v>
+        <v>1.457362352084697</v>
       </c>
     </row>
     <row r="29">
@@ -2796,22 +2796,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3.559655103991918</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="D29" t="n">
-        <v>6528</v>
+        <v>6696</v>
       </c>
       <c r="E29" t="n">
-        <v>2.063112745098039</v>
+        <v>2.011519607843137</v>
       </c>
       <c r="F29" t="n">
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>1.496542358893879</v>
+        <v>1.46241853285817</v>
       </c>
     </row>
     <row r="30">
@@ -2821,22 +2821,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>3.789291932327125</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="D30" t="n">
-        <v>4904</v>
+        <v>6528</v>
       </c>
       <c r="E30" t="n">
-        <v>2.349938725490196</v>
+        <v>2.063112745098039</v>
       </c>
       <c r="F30" t="n">
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>1.439353206836929</v>
+        <v>1.496542358893879</v>
       </c>
     </row>
     <row r="31">
@@ -2846,22 +2846,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>3.866575385749644</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="D31" t="n">
-        <v>3744</v>
+        <v>4904</v>
       </c>
       <c r="E31" t="n">
-        <v>2.55735294117647</v>
+        <v>2.349938725490196</v>
       </c>
       <c r="F31" t="n">
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>1.309222444573174</v>
+        <v>1.439353206836929</v>
       </c>
     </row>
     <row r="32">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>3.927499916586033</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="D32" t="n">
-        <v>5304</v>
+        <v>3744</v>
       </c>
       <c r="E32" t="n">
-        <v>2.578799019607843</v>
+        <v>2.55735294117647</v>
       </c>
       <c r="F32" t="n">
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>1.34870089697819</v>
+        <v>1.309222444573174</v>
       </c>
     </row>
     <row r="33">
@@ -2896,22 +2896,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>3.996886296418009</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="D33" t="n">
-        <v>6456</v>
+        <v>5304</v>
       </c>
       <c r="E33" t="n">
-        <v>2.506740196078431</v>
+        <v>2.578799019607843</v>
       </c>
       <c r="F33" t="n">
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>1.490146100339577</v>
+        <v>1.34870089697819</v>
       </c>
     </row>
     <row r="34">
@@ -2921,22 +2921,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>4.173726067180183</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="D34" t="n">
-        <v>6136</v>
+        <v>6456</v>
       </c>
       <c r="E34" t="n">
-        <v>2.735294117647058</v>
+        <v>2.506740196078431</v>
       </c>
       <c r="F34" t="n">
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>1.438431949533124</v>
+        <v>1.490146100339577</v>
       </c>
     </row>
     <row r="35">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>4.104804034498446</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="D35" t="n">
-        <v>6088</v>
+        <v>6136</v>
       </c>
       <c r="E35" t="n">
-        <v>2.709681372549019</v>
+        <v>2.735294117647058</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>1.395122661949427</v>
+        <v>1.438431949533124</v>
       </c>
     </row>
     <row r="36">
@@ -2971,21 +2971,46 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6088</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.709681372549019</v>
+      </c>
+      <c r="F36" t="n">
+        <v>96</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.395122661949427</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>9</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>7408</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>2.733639705882353</v>
       </c>
-      <c r="F36" t="n">
-        <v>96</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F37" t="n">
+        <v>96</v>
+      </c>
+      <c r="G37" t="n">
         <v>1.586795239450864</v>
       </c>
     </row>

--- a/Exp3_PTO_GRPO/eda/results/arms/training/tables/claude-haiku-4-5/training.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/training/tables/claude-haiku-4-5/training.xlsx
@@ -453,7 +453,7 @@
         <v>0.7599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.804</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>0.8037</v>
@@ -470,7 +470,7 @@
         <v>0.7707000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8244</v>
       </c>
       <c r="D3" t="n">
         <v>0.8037</v>
@@ -487,7 +487,7 @@
         <v>0.7736</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8144</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="D4" t="n">
         <v>0.7961</v>
@@ -504,7 +504,7 @@
         <v>0.7562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8224</v>
       </c>
       <c r="D5" t="n">
         <v>0.7883</v>
@@ -521,7 +521,7 @@
         <v>0.7474</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8141</v>
+        <v>0.8199</v>
       </c>
       <c r="D6" t="n">
         <v>0.7758</v>
@@ -538,7 +538,7 @@
         <v>0.7359</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8118</v>
+        <v>0.8172</v>
       </c>
       <c r="D7" t="n">
         <v>0.7708</v>
@@ -555,7 +555,7 @@
         <v>0.7292999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8189</v>
       </c>
       <c r="D8" t="n">
         <v>0.7534999999999999</v>
@@ -572,7 +572,7 @@
         <v>0.7281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8179</v>
+        <v>0.8202</v>
       </c>
       <c r="D9" t="n">
         <v>0.7468</v>
@@ -589,7 +589,7 @@
         <v>0.7211</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8189</v>
+        <v>0.819</v>
       </c>
       <c r="D10" t="n">
         <v>0.7413</v>
@@ -606,7 +606,7 @@
         <v>0.7229</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8157</v>
+        <v>0.8133</v>
       </c>
       <c r="D11" t="n">
         <v>0.7168</v>
@@ -623,7 +623,7 @@
         <v>0.7131</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8123</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>0.7224</v>
@@ -640,7 +640,7 @@
         <v>0.7138</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8197</v>
+        <v>0.8088</v>
       </c>
       <c r="D13" t="n">
         <v>0.7217</v>
@@ -657,7 +657,7 @@
         <v>0.7222</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8252</v>
+        <v>0.8137</v>
       </c>
       <c r="D14" t="n">
         <v>0.7277</v>
@@ -674,7 +674,7 @@
         <v>0.709</v>
       </c>
       <c r="C15" t="n">
-        <v>0.829</v>
+        <v>0.8056</v>
       </c>
       <c r="D15" t="n">
         <v>0.7292</v>
@@ -691,7 +691,7 @@
         <v>0.7144</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8378</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>0.7262999999999999</v>
@@ -708,7 +708,7 @@
         <v>0.7217</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8328</v>
+        <v>0.8167</v>
       </c>
       <c r="D17" t="n">
         <v>0.7118</v>
@@ -725,7 +725,7 @@
         <v>0.7102000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8259</v>
+        <v>0.8102</v>
       </c>
       <c r="D18" t="n">
         <v>0.7069</v>
@@ -742,7 +742,7 @@
         <v>0.7093</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8272</v>
+        <v>0.8179</v>
       </c>
       <c r="D19" t="n">
         <v>0.7036</v>
@@ -759,7 +759,7 @@
         <v>0.7171</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8247</v>
+        <v>0.8161</v>
       </c>
       <c r="D20" t="n">
         <v>0.7027</v>
@@ -776,7 +776,7 @@
         <v>0.7189</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8359</v>
+        <v>0.8243</v>
       </c>
     </row>
   </sheetData>
@@ -1145,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8040124095139607</v>
+        <v>0.8120329902720993</v>
       </c>
       <c r="D22" t="n">
-        <v>24175</v>
+        <v>28372</v>
       </c>
     </row>
     <row r="23">
@@ -1161,10 +1161,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8169719330610093</v>
+        <v>0.8244494214259052</v>
       </c>
       <c r="D23" t="n">
-        <v>22767</v>
+        <v>26790</v>
       </c>
     </row>
     <row r="24">
@@ -1177,10 +1177,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.814419878693015</v>
+        <v>0.8201142665098303</v>
       </c>
       <c r="D24" t="n">
-        <v>20444</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="25">
@@ -1193,10 +1193,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.813967635965446</v>
+        <v>0.8224308655276794</v>
       </c>
       <c r="D25" t="n">
-        <v>16438</v>
+        <v>19491</v>
       </c>
     </row>
     <row r="26">
@@ -1209,10 +1209,10 @@
         <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8141448645291515</v>
+        <v>0.8199315378156687</v>
       </c>
       <c r="D26" t="n">
-        <v>12881</v>
+        <v>15483</v>
       </c>
     </row>
     <row r="27">
@@ -1225,10 +1225,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8118179946469014</v>
+        <v>0.8171710416318342</v>
       </c>
       <c r="D27" t="n">
-        <v>9714</v>
+        <v>11962</v>
       </c>
     </row>
     <row r="28">
@@ -1241,10 +1241,10 @@
         <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.817021873247336</v>
+        <v>0.8188591385331782</v>
       </c>
       <c r="D28" t="n">
-        <v>7132</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="29">
@@ -1257,10 +1257,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8178838098706975</v>
+        <v>0.820170837704181</v>
       </c>
       <c r="D29" t="n">
-        <v>5491</v>
+        <v>6673</v>
       </c>
     </row>
     <row r="30">
@@ -1273,10 +1273,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8188976377952756</v>
+        <v>0.8190284879474069</v>
       </c>
       <c r="D30" t="n">
-        <v>4572</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="31">
@@ -1289,10 +1289,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8156643356643357</v>
+        <v>0.813279962326348</v>
       </c>
       <c r="D31" t="n">
-        <v>3575</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="32">
@@ -1305,10 +1305,10 @@
         <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8122634367903103</v>
+        <v>0.8099547511312217</v>
       </c>
       <c r="D32" t="n">
-        <v>2642</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="33">
@@ -1321,10 +1321,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8196642685851319</v>
+        <v>0.808768267223382</v>
       </c>
       <c r="D33" t="n">
-        <v>2085</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="34">
@@ -1337,10 +1337,10 @@
         <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8252321135991262</v>
+        <v>0.8137440758293839</v>
       </c>
       <c r="D34" t="n">
-        <v>1831</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="35">
@@ -1353,10 +1353,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8289835164835165</v>
+        <v>0.8056052474657126</v>
       </c>
       <c r="D35" t="n">
-        <v>1456</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="36">
@@ -1369,10 +1369,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8378170637970792</v>
+        <v>0.8211163416274377</v>
       </c>
       <c r="D36" t="n">
-        <v>1301</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="37">
@@ -1385,10 +1385,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8327645051194539</v>
+        <v>0.816679188580015</v>
       </c>
       <c r="D37" t="n">
-        <v>1172</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="38">
@@ -1401,10 +1401,10 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>0.825922421948912</v>
+        <v>0.8101889893179951</v>
       </c>
       <c r="D38" t="n">
-        <v>1057</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="39">
@@ -1417,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.8178603006189213</v>
       </c>
       <c r="D39" t="n">
-        <v>972</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="40">
@@ -1433,10 +1433,10 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.824654622741764</v>
+        <v>0.8161137440758294</v>
       </c>
       <c r="D40" t="n">
-        <v>941</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="41">
@@ -1449,10 +1449,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>0.835909631391201</v>
+        <v>0.8242811501597445</v>
       </c>
       <c r="D41" t="n">
-        <v>841</v>
+        <v>939</v>
       </c>
     </row>
     <row r="42">
@@ -2074,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,26 +2517,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>3.290739216204042</v>
+        <v>4.112989772033381</v>
       </c>
       <c r="D18" t="n">
-        <v>7592</v>
+        <v>9248</v>
       </c>
       <c r="E18" t="n">
-        <v>1.829718137254902</v>
+        <v>2.903308823529412</v>
       </c>
       <c r="F18" t="n">
         <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46102107894914</v>
+        <v>1.209680948503969</v>
       </c>
     </row>
     <row r="19">
@@ -2546,22 +2546,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3.33243209735256</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="D19" t="n">
-        <v>6176</v>
+        <v>7592</v>
       </c>
       <c r="E19" t="n">
-        <v>2.071568627450981</v>
+        <v>1.829718137254902</v>
       </c>
       <c r="F19" t="n">
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>1.260863469901579</v>
+        <v>1.46102107894914</v>
       </c>
     </row>
     <row r="20">
@@ -2571,22 +2571,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.536591102906034</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="D20" t="n">
-        <v>6296</v>
+        <v>6176</v>
       </c>
       <c r="E20" t="n">
-        <v>2.199203431372549</v>
+        <v>2.071568627450981</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>1.337387671533485</v>
+        <v>1.260863469901579</v>
       </c>
     </row>
     <row r="21">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>3.663854489164087</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="D21" t="n">
-        <v>5176</v>
+        <v>6296</v>
       </c>
       <c r="E21" t="n">
-        <v>2.480208333333333</v>
+        <v>2.199203431372549</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>1.183646155830754</v>
+        <v>1.337387671533485</v>
       </c>
     </row>
     <row r="22">
@@ -2621,22 +2621,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3.743944564470195</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="D22" t="n">
-        <v>4800</v>
+        <v>5176</v>
       </c>
       <c r="E22" t="n">
-        <v>2.680453431372549</v>
+        <v>2.480208333333333</v>
       </c>
       <c r="F22" t="n">
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>1.063491133097647</v>
+        <v>1.183646155830754</v>
       </c>
     </row>
     <row r="23">
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3.776677555295115</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="D23" t="n">
-        <v>4728</v>
+        <v>4800</v>
       </c>
       <c r="E23" t="n">
-        <v>2.751960784313725</v>
+        <v>2.680453431372549</v>
       </c>
       <c r="F23" t="n">
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>1.024716770981389</v>
+        <v>1.063491133097647</v>
       </c>
     </row>
     <row r="24">
@@ -2671,22 +2671,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>3.889255298078827</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="D24" t="n">
-        <v>4168</v>
+        <v>4728</v>
       </c>
       <c r="E24" t="n">
-        <v>2.849571078431373</v>
+        <v>2.751960784313725</v>
       </c>
       <c r="F24" t="n">
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>1.039684219647455</v>
+        <v>1.024716770981389</v>
       </c>
     </row>
     <row r="25">
@@ -2696,22 +2696,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4.005326146015042</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="D25" t="n">
-        <v>4136</v>
+        <v>4168</v>
       </c>
       <c r="E25" t="n">
-        <v>2.813235294117647</v>
+        <v>2.849571078431373</v>
       </c>
       <c r="F25" t="n">
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>1.192090851897395</v>
+        <v>1.039684219647455</v>
       </c>
     </row>
     <row r="26">
@@ -2721,22 +2721,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3.999240719910011</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="D26" t="n">
-        <v>3568</v>
+        <v>4136</v>
       </c>
       <c r="E26" t="n">
-        <v>2.895465686274509</v>
+        <v>2.813235294117647</v>
       </c>
       <c r="F26" t="n">
         <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>1.103775033635502</v>
+        <v>1.192090851897395</v>
       </c>
     </row>
     <row r="27">
@@ -2746,47 +2746,47 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>4.077670148096037</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="D27" t="n">
-        <v>3280</v>
+        <v>3568</v>
       </c>
       <c r="E27" t="n">
-        <v>2.921078431372549</v>
+        <v>2.895465686274509</v>
       </c>
       <c r="F27" t="n">
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>1.156591716723488</v>
+        <v>1.103775033635502</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>3.291063332476854</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="D28" t="n">
-        <v>7120</v>
+        <v>3280</v>
       </c>
       <c r="E28" t="n">
-        <v>1.833700980392157</v>
+        <v>2.921078431372549</v>
       </c>
       <c r="F28" t="n">
         <v>96</v>
       </c>
       <c r="G28" t="n">
-        <v>1.457362352084697</v>
+        <v>1.156591716723488</v>
       </c>
     </row>
     <row r="29">
@@ -2796,22 +2796,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>3.473938140701307</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="D29" t="n">
-        <v>6696</v>
+        <v>7120</v>
       </c>
       <c r="E29" t="n">
-        <v>2.011519607843137</v>
+        <v>1.833700980392157</v>
       </c>
       <c r="F29" t="n">
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>1.46241853285817</v>
+        <v>1.457362352084697</v>
       </c>
     </row>
     <row r="30">
@@ -2821,22 +2821,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3.559655103991918</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="D30" t="n">
-        <v>6528</v>
+        <v>6696</v>
       </c>
       <c r="E30" t="n">
-        <v>2.063112745098039</v>
+        <v>2.011519607843137</v>
       </c>
       <c r="F30" t="n">
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>1.496542358893879</v>
+        <v>1.46241853285817</v>
       </c>
     </row>
     <row r="31">
@@ -2846,22 +2846,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>3.789291932327125</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="D31" t="n">
-        <v>4904</v>
+        <v>6528</v>
       </c>
       <c r="E31" t="n">
-        <v>2.349938725490196</v>
+        <v>2.063112745098039</v>
       </c>
       <c r="F31" t="n">
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>1.439353206836929</v>
+        <v>1.496542358893879</v>
       </c>
     </row>
     <row r="32">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>3.866575385749644</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="D32" t="n">
-        <v>3744</v>
+        <v>4904</v>
       </c>
       <c r="E32" t="n">
-        <v>2.55735294117647</v>
+        <v>2.349938725490196</v>
       </c>
       <c r="F32" t="n">
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>1.309222444573174</v>
+        <v>1.439353206836929</v>
       </c>
     </row>
     <row r="33">
@@ -2896,22 +2896,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>3.927499916586033</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="D33" t="n">
-        <v>5304</v>
+        <v>3744</v>
       </c>
       <c r="E33" t="n">
-        <v>2.578799019607843</v>
+        <v>2.55735294117647</v>
       </c>
       <c r="F33" t="n">
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>1.34870089697819</v>
+        <v>1.309222444573174</v>
       </c>
     </row>
     <row r="34">
@@ -2921,22 +2921,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>3.996886296418009</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="D34" t="n">
-        <v>6456</v>
+        <v>5304</v>
       </c>
       <c r="E34" t="n">
-        <v>2.506740196078431</v>
+        <v>2.578799019607843</v>
       </c>
       <c r="F34" t="n">
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>1.490146100339577</v>
+        <v>1.34870089697819</v>
       </c>
     </row>
     <row r="35">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>4.173726067180183</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="D35" t="n">
-        <v>6136</v>
+        <v>6456</v>
       </c>
       <c r="E35" t="n">
-        <v>2.735294117647058</v>
+        <v>2.506740196078431</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>1.438431949533124</v>
+        <v>1.490146100339577</v>
       </c>
     </row>
     <row r="36">
@@ -2971,22 +2971,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>4.104804034498446</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="D36" t="n">
-        <v>6088</v>
+        <v>6136</v>
       </c>
       <c r="E36" t="n">
-        <v>2.709681372549019</v>
+        <v>2.735294117647058</v>
       </c>
       <c r="F36" t="n">
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>1.395122661949427</v>
+        <v>1.438431949533124</v>
       </c>
     </row>
     <row r="37">
@@ -2996,21 +2996,46 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6088</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.709681372549019</v>
+      </c>
+      <c r="F37" t="n">
+        <v>96</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.395122661949427</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
         <v>9</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>7408</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E38" t="n">
         <v>2.733639705882353</v>
       </c>
-      <c r="F37" t="n">
-        <v>96</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F38" t="n">
+        <v>96</v>
+      </c>
+      <c r="G38" t="n">
         <v>1.586795239450864</v>
       </c>
     </row>

--- a/Exp3_PTO_GRPO/eda/results/arms/training/tables/claude-haiku-4-5/training.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/training/tables/claude-haiku-4-5/training.xlsx
@@ -453,7 +453,7 @@
         <v>0.7599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7987</v>
       </c>
       <c r="D2" t="n">
         <v>0.8037</v>
@@ -470,7 +470,7 @@
         <v>0.7707000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8244</v>
+        <v>0.8084</v>
       </c>
       <c r="D3" t="n">
         <v>0.8037</v>
@@ -487,7 +487,7 @@
         <v>0.7736</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8058</v>
       </c>
       <c r="D4" t="n">
         <v>0.7961</v>
@@ -504,7 +504,7 @@
         <v>0.7562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8224</v>
+        <v>0.8024</v>
       </c>
       <c r="D5" t="n">
         <v>0.7883</v>
@@ -521,7 +521,7 @@
         <v>0.7474</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8199</v>
+        <v>0.7983</v>
       </c>
       <c r="D6" t="n">
         <v>0.7758</v>
@@ -538,7 +538,7 @@
         <v>0.7359</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8172</v>
+        <v>0.7972</v>
       </c>
       <c r="D7" t="n">
         <v>0.7708</v>
@@ -555,7 +555,7 @@
         <v>0.7292999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8189</v>
+        <v>0.7988</v>
       </c>
       <c r="D8" t="n">
         <v>0.7534999999999999</v>
@@ -572,7 +572,7 @@
         <v>0.7281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8202</v>
+        <v>0.8026</v>
       </c>
       <c r="D9" t="n">
         <v>0.7468</v>
@@ -589,7 +589,7 @@
         <v>0.7211</v>
       </c>
       <c r="C10" t="n">
-        <v>0.819</v>
+        <v>0.7994</v>
       </c>
       <c r="D10" t="n">
         <v>0.7413</v>
@@ -606,7 +606,7 @@
         <v>0.7229</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8133</v>
+        <v>0.7904</v>
       </c>
       <c r="D11" t="n">
         <v>0.7168</v>
@@ -623,7 +623,7 @@
         <v>0.7131</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7915</v>
       </c>
       <c r="D12" t="n">
         <v>0.7224</v>
@@ -640,7 +640,7 @@
         <v>0.7138</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8088</v>
+        <v>0.7896</v>
       </c>
       <c r="D13" t="n">
         <v>0.7217</v>
@@ -657,7 +657,7 @@
         <v>0.7222</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8137</v>
+        <v>0.7842</v>
       </c>
       <c r="D14" t="n">
         <v>0.7277</v>
@@ -674,7 +674,7 @@
         <v>0.709</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8056</v>
+        <v>0.786</v>
       </c>
       <c r="D15" t="n">
         <v>0.7292</v>
@@ -691,7 +691,7 @@
         <v>0.7144</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.788</v>
       </c>
       <c r="D16" t="n">
         <v>0.7262999999999999</v>
@@ -708,7 +708,7 @@
         <v>0.7217</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8167</v>
+        <v>0.7877</v>
       </c>
       <c r="D17" t="n">
         <v>0.7118</v>
@@ -725,7 +725,7 @@
         <v>0.7102000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8102</v>
+        <v>0.7743</v>
       </c>
       <c r="D18" t="n">
         <v>0.7069</v>
@@ -742,7 +742,7 @@
         <v>0.7093</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8179</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>0.7036</v>
@@ -759,7 +759,7 @@
         <v>0.7171</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8161</v>
+        <v>0.7904</v>
       </c>
       <c r="D20" t="n">
         <v>0.7027</v>
@@ -776,7 +776,7 @@
         <v>0.7189</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8243</v>
+        <v>0.7972</v>
       </c>
     </row>
   </sheetData>
@@ -1145,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8120329902720993</v>
+        <v>0.798689988469936</v>
       </c>
       <c r="D22" t="n">
-        <v>28372</v>
+        <v>40763</v>
       </c>
     </row>
     <row r="23">
@@ -1161,10 +1161,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8244494214259052</v>
+        <v>0.8083985473888804</v>
       </c>
       <c r="D23" t="n">
-        <v>26790</v>
+        <v>39102</v>
       </c>
     </row>
     <row r="24">
@@ -1177,10 +1177,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8201142665098303</v>
+        <v>0.8057545775048334</v>
       </c>
       <c r="D24" t="n">
-        <v>23804</v>
+        <v>35172</v>
       </c>
     </row>
     <row r="25">
@@ -1193,10 +1193,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8224308655276794</v>
+        <v>0.802425691834643</v>
       </c>
       <c r="D25" t="n">
-        <v>19491</v>
+        <v>29270</v>
       </c>
     </row>
     <row r="26">
@@ -1209,10 +1209,10 @@
         <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8199315378156687</v>
+        <v>0.798336008108793</v>
       </c>
       <c r="D26" t="n">
-        <v>15483</v>
+        <v>23678</v>
       </c>
     </row>
     <row r="27">
@@ -1225,10 +1225,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8171710416318342</v>
+        <v>0.7971563981042654</v>
       </c>
       <c r="D27" t="n">
-        <v>11962</v>
+        <v>18990</v>
       </c>
     </row>
     <row r="28">
@@ -1241,10 +1241,10 @@
         <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8188591385331782</v>
+        <v>0.7988340290772995</v>
       </c>
       <c r="D28" t="n">
-        <v>8590</v>
+        <v>13894</v>
       </c>
     </row>
     <row r="29">
@@ -1257,10 +1257,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.820170837704181</v>
+        <v>0.8025661877654288</v>
       </c>
       <c r="D29" t="n">
-        <v>6673</v>
+        <v>11067</v>
       </c>
     </row>
     <row r="30">
@@ -1273,10 +1273,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8190284879474069</v>
+        <v>0.7994395947839207</v>
       </c>
       <c r="D30" t="n">
-        <v>5476</v>
+        <v>9279</v>
       </c>
     </row>
     <row r="31">
@@ -1289,10 +1289,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.813279962326348</v>
+        <v>0.7903555373927258</v>
       </c>
       <c r="D31" t="n">
-        <v>4247</v>
+        <v>7341</v>
       </c>
     </row>
     <row r="32">
@@ -1305,10 +1305,10 @@
         <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8099547511312217</v>
+        <v>0.7915085817524842</v>
       </c>
       <c r="D32" t="n">
-        <v>3094</v>
+        <v>5535</v>
       </c>
     </row>
     <row r="33">
@@ -1321,10 +1321,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.808768267223382</v>
+        <v>0.789600702062308</v>
       </c>
       <c r="D33" t="n">
-        <v>2395</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="34">
@@ -1337,10 +1337,10 @@
         <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8137440758293839</v>
+        <v>0.7842023748064016</v>
       </c>
       <c r="D34" t="n">
-        <v>2110</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="35">
@@ -1353,10 +1353,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8056052474657126</v>
+        <v>0.7860043736332396</v>
       </c>
       <c r="D35" t="n">
-        <v>1677</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="36">
@@ -1369,10 +1369,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8211163416274377</v>
+        <v>0.7880101119537739</v>
       </c>
       <c r="D36" t="n">
-        <v>1487</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="37">
@@ -1385,10 +1385,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.816679188580015</v>
+        <v>0.7876739562624254</v>
       </c>
       <c r="D37" t="n">
-        <v>1331</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="38">
@@ -1401,10 +1401,10 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8101889893179951</v>
+        <v>0.7743207712532866</v>
       </c>
       <c r="D38" t="n">
-        <v>1217</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="39">
@@ -1417,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8178603006189213</v>
+        <v>0.7888227210261108</v>
       </c>
       <c r="D39" t="n">
-        <v>1131</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="40">
@@ -1433,10 +1433,10 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8161137440758294</v>
+        <v>0.7903951975987994</v>
       </c>
       <c r="D40" t="n">
-        <v>1055</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="41">
@@ -1449,10 +1449,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8242811501597445</v>
+        <v>0.7972067039106145</v>
       </c>
       <c r="D41" t="n">
-        <v>939</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="42">
@@ -2074,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2542,76 +2542,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>3.290739216204042</v>
+        <v>4.093557233704293</v>
       </c>
       <c r="D19" t="n">
-        <v>7592</v>
+        <v>14800</v>
       </c>
       <c r="E19" t="n">
-        <v>1.829718137254902</v>
+        <v>2.912009803921569</v>
       </c>
       <c r="F19" t="n">
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46102107894914</v>
+        <v>1.181547429782724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>3.33243209735256</v>
+        <v>4.256488492237043</v>
       </c>
       <c r="D20" t="n">
-        <v>6176</v>
+        <v>17216</v>
       </c>
       <c r="E20" t="n">
-        <v>2.071568627450981</v>
+        <v>2.775735294117647</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>1.260863469901579</v>
+        <v>1.480753198119396</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>3.536591102906034</v>
+        <v>4.452882443798349</v>
       </c>
       <c r="D21" t="n">
-        <v>6296</v>
+        <v>18128</v>
       </c>
       <c r="E21" t="n">
-        <v>2.199203431372549</v>
+        <v>2.858272058823529</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>1.337387671533485</v>
+        <v>1.59461038497482</v>
       </c>
     </row>
     <row r="22">
@@ -2621,22 +2621,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3.663854489164087</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="D22" t="n">
-        <v>5176</v>
+        <v>7592</v>
       </c>
       <c r="E22" t="n">
-        <v>2.480208333333333</v>
+        <v>1.829718137254902</v>
       </c>
       <c r="F22" t="n">
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>1.183646155830754</v>
+        <v>1.46102107894914</v>
       </c>
     </row>
     <row r="23">
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.743944564470195</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="D23" t="n">
-        <v>4800</v>
+        <v>6176</v>
       </c>
       <c r="E23" t="n">
-        <v>2.680453431372549</v>
+        <v>2.071568627450981</v>
       </c>
       <c r="F23" t="n">
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>1.063491133097647</v>
+        <v>1.260863469901579</v>
       </c>
     </row>
     <row r="24">
@@ -2671,22 +2671,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>3.776677555295115</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="D24" t="n">
-        <v>4728</v>
+        <v>6296</v>
       </c>
       <c r="E24" t="n">
-        <v>2.751960784313725</v>
+        <v>2.199203431372549</v>
       </c>
       <c r="F24" t="n">
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>1.024716770981389</v>
+        <v>1.337387671533485</v>
       </c>
     </row>
     <row r="25">
@@ -2696,22 +2696,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>3.889255298078827</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="D25" t="n">
-        <v>4168</v>
+        <v>5176</v>
       </c>
       <c r="E25" t="n">
-        <v>2.849571078431373</v>
+        <v>2.480208333333333</v>
       </c>
       <c r="F25" t="n">
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>1.039684219647455</v>
+        <v>1.183646155830754</v>
       </c>
     </row>
     <row r="26">
@@ -2721,22 +2721,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4.005326146015042</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="D26" t="n">
-        <v>4136</v>
+        <v>4800</v>
       </c>
       <c r="E26" t="n">
-        <v>2.813235294117647</v>
+        <v>2.680453431372549</v>
       </c>
       <c r="F26" t="n">
         <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>1.192090851897395</v>
+        <v>1.063491133097647</v>
       </c>
     </row>
     <row r="27">
@@ -2746,22 +2746,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>3.999240719910011</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="D27" t="n">
-        <v>3568</v>
+        <v>4728</v>
       </c>
       <c r="E27" t="n">
-        <v>2.895465686274509</v>
+        <v>2.751960784313725</v>
       </c>
       <c r="F27" t="n">
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>1.103775033635502</v>
+        <v>1.024716770981389</v>
       </c>
     </row>
     <row r="28">
@@ -2771,97 +2771,97 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>4.077670148096037</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="D28" t="n">
-        <v>3280</v>
+        <v>4168</v>
       </c>
       <c r="E28" t="n">
-        <v>2.921078431372549</v>
+        <v>2.849571078431373</v>
       </c>
       <c r="F28" t="n">
         <v>96</v>
       </c>
       <c r="G28" t="n">
-        <v>1.156591716723488</v>
+        <v>1.039684219647455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>3.291063332476854</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="D29" t="n">
-        <v>7120</v>
+        <v>4136</v>
       </c>
       <c r="E29" t="n">
-        <v>1.833700980392157</v>
+        <v>2.813235294117647</v>
       </c>
       <c r="F29" t="n">
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>1.457362352084697</v>
+        <v>1.192090851897395</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>3.473938140701307</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="D30" t="n">
-        <v>6696</v>
+        <v>3568</v>
       </c>
       <c r="E30" t="n">
-        <v>2.011519607843137</v>
+        <v>2.895465686274509</v>
       </c>
       <c r="F30" t="n">
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>1.46241853285817</v>
+        <v>1.103775033635502</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>3.559655103991918</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="D31" t="n">
-        <v>6528</v>
+        <v>3280</v>
       </c>
       <c r="E31" t="n">
-        <v>2.063112745098039</v>
+        <v>2.921078431372549</v>
       </c>
       <c r="F31" t="n">
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>1.496542358893879</v>
+        <v>1.156591716723488</v>
       </c>
     </row>
     <row r="32">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>3.789291932327125</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="D32" t="n">
-        <v>4904</v>
+        <v>7120</v>
       </c>
       <c r="E32" t="n">
-        <v>2.349938725490196</v>
+        <v>1.833700980392157</v>
       </c>
       <c r="F32" t="n">
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>1.439353206836929</v>
+        <v>1.457362352084697</v>
       </c>
     </row>
     <row r="33">
@@ -2896,22 +2896,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3.866575385749644</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="D33" t="n">
-        <v>3744</v>
+        <v>6696</v>
       </c>
       <c r="E33" t="n">
-        <v>2.55735294117647</v>
+        <v>2.011519607843137</v>
       </c>
       <c r="F33" t="n">
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>1.309222444573174</v>
+        <v>1.46241853285817</v>
       </c>
     </row>
     <row r="34">
@@ -2921,22 +2921,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>3.927499916586033</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="D34" t="n">
-        <v>5304</v>
+        <v>6528</v>
       </c>
       <c r="E34" t="n">
-        <v>2.578799019607843</v>
+        <v>2.063112745098039</v>
       </c>
       <c r="F34" t="n">
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>1.34870089697819</v>
+        <v>1.496542358893879</v>
       </c>
     </row>
     <row r="35">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>3.996886296418009</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="D35" t="n">
-        <v>6456</v>
+        <v>4904</v>
       </c>
       <c r="E35" t="n">
-        <v>2.506740196078431</v>
+        <v>2.349938725490196</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>1.490146100339577</v>
+        <v>1.439353206836929</v>
       </c>
     </row>
     <row r="36">
@@ -2971,22 +2971,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>4.173726067180183</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="D36" t="n">
-        <v>6136</v>
+        <v>3744</v>
       </c>
       <c r="E36" t="n">
-        <v>2.735294117647058</v>
+        <v>2.55735294117647</v>
       </c>
       <c r="F36" t="n">
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>1.438431949533124</v>
+        <v>1.309222444573174</v>
       </c>
     </row>
     <row r="37">
@@ -2996,22 +2996,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>4.104804034498446</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="D37" t="n">
-        <v>6088</v>
+        <v>5304</v>
       </c>
       <c r="E37" t="n">
-        <v>2.709681372549019</v>
+        <v>2.578799019607843</v>
       </c>
       <c r="F37" t="n">
         <v>96</v>
       </c>
       <c r="G37" t="n">
-        <v>1.395122661949427</v>
+        <v>1.34870089697819</v>
       </c>
     </row>
     <row r="38">
@@ -3021,21 +3021,96 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.996886296418009</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6456</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.506740196078431</v>
+      </c>
+      <c r="F38" t="n">
+        <v>96</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.490146100339577</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.173726067180183</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6136</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.735294117647058</v>
+      </c>
+      <c r="F39" t="n">
+        <v>96</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.438431949533124</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6088</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.709681372549019</v>
+      </c>
+      <c r="F40" t="n">
+        <v>96</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.395122661949427</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
         <v>9</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C41" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D41" t="n">
         <v>7408</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E41" t="n">
         <v>2.733639705882353</v>
       </c>
-      <c r="F38" t="n">
-        <v>96</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F41" t="n">
+        <v>96</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.586795239450864</v>
       </c>
     </row>
